--- a/data/trans_dic/P22$mutuaSPriv-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P22$mutuaSPriv-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Mutualidad de Estado (Privado)</t>
+          <t>Población que, al menos, es beneficiaria de mutualidades del Estado (seguro privado) (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,55</t>
+          <t>0,85; 2,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,3</t>
+          <t>0,1; 1,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,88</t>
+          <t>0,64; 1,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,38</t>
+          <t>0,3; 1,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,09</t>
+          <t>0,13; 1,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,3</t>
+          <t>0,25; 1,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,84</t>
+          <t>0,92; 1,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,09</t>
+          <t>0,31; 1,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,8</t>
+          <t>0,14; 0,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,74</t>
+          <t>0,17; 0,73</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,78</t>
+          <t>1,38; 2,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,43</t>
+          <t>1,78; 3,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,26</t>
+          <t>1,06; 2,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,24</t>
+          <t>1,49; 3,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,63</t>
+          <t>1,22; 2,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,46</t>
+          <t>1,06; 2,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,66</t>
+          <t>0,64; 1,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,99</t>
+          <t>0,93; 1,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,44</t>
+          <t>1,48; 2,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,7</t>
+          <t>1,62; 2,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,75</t>
+          <t>0,98; 1,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,43</t>
+          <t>1,37; 2,42</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,8</t>
+          <t>2,42; 5,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 7,85</t>
+          <t>3,0; 7,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,53; 9,06</t>
+          <t>4,64; 9,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,3; 8,12</t>
+          <t>4,33; 8,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 7,64</t>
+          <t>3,4; 7,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,05; 9,37</t>
+          <t>4,08; 9,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 8,12</t>
+          <t>4,23; 8,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,26; 10,54</t>
+          <t>6,36; 10,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,01</t>
+          <t>3,25; 6,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,89; 7,2</t>
+          <t>4,02; 7,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 8,1</t>
+          <t>4,83; 7,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,82; 8,53</t>
+          <t>5,84; 8,5</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,7</t>
+          <t>1,67; 2,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,81</t>
+          <t>1,74; 2,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,69</t>
+          <t>1,58; 2,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,44</t>
+          <t>2,01; 3,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,61</t>
+          <t>1,59; 2,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,44</t>
+          <t>1,37; 2,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,18</t>
+          <t>1,3; 2,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,0</t>
+          <t>1,92; 2,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 2,49</t>
+          <t>1,74; 2,45</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,43</t>
+          <t>1,68; 2,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,25</t>
+          <t>1,54; 2,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 2,95</t>
+          <t>2,09; 3,0</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Mutualidad de Estado (Privado)</t>
+          <t>Población que, al menos, es beneficiaria de mutualidades del Estado (seguro privado) (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8984; 26269</t>
+          <t>8781; 25576</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1016; 12708</t>
+          <t>1019; 12742</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6769</t>
+          <t>0; 7354</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2345</t>
+          <t>0; 2380</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8254; 24720</t>
+          <t>8414; 25043</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4222; 18467</t>
+          <t>4036; 19206</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1271; 10811</t>
+          <t>1272; 11494</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1624; 9793</t>
+          <t>1907; 9030</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21762; 43101</t>
+          <t>21672; 43141</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7161; 25127</t>
+          <t>7241; 23997</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2406; 13990</t>
+          <t>2405; 13362</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2114; 9368</t>
+          <t>2144; 9231</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22612; 47037</t>
+          <t>23267; 48132</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34572; 67333</t>
+          <t>34853; 65913</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21114; 46801</t>
+          <t>21989; 46864</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34566; 74182</t>
+          <t>34156; 74580</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19256; 41713</t>
+          <t>19349; 42545</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19218; 43234</t>
+          <t>18586; 42750</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12169; 33012</t>
+          <t>12770; 34079</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20289; 44633</t>
+          <t>20716; 44121</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47681; 79893</t>
+          <t>48638; 81839</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59880; 100415</t>
+          <t>60292; 98352</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38957; 71193</t>
+          <t>39772; 70608</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>62890; 110245</t>
+          <t>62157; 109573</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13950; 31957</t>
+          <t>13358; 32095</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13922; 37759</t>
+          <t>14429; 36894</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24749; 49474</t>
+          <t>25330; 51279</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27817; 52486</t>
+          <t>28008; 52582</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16108; 36407</t>
+          <t>16210; 36740</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18576; 42974</t>
+          <t>18713; 42716</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23015; 44615</t>
+          <t>23226; 45487</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>41318; 69614</t>
+          <t>42000; 66871</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34107; 61785</t>
+          <t>33365; 61834</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36559; 67620</t>
+          <t>37765; 69328</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54241; 88666</t>
+          <t>52897; 87040</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>76054; 111548</t>
+          <t>76357; 111160</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>54170; 88277</t>
+          <t>54737; 89218</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>58999; 96079</t>
+          <t>59320; 95835</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54538; 90639</t>
+          <t>53156; 90118</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69955; 118577</t>
+          <t>69537; 117775</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54954; 88275</t>
+          <t>53667; 87804</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>51166; 86582</t>
+          <t>48831; 88026</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45103; 76714</t>
+          <t>45793; 76045</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69450; 109512</t>
+          <t>70133; 109175</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>117526; 165710</t>
+          <t>115980; 162688</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>115993; 169274</t>
+          <t>117070; 170972</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>108602; 155015</t>
+          <t>106281; 155511</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>147697; 209814</t>
+          <t>148520; 213200</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$mutuaSPriv-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P22$mutuaSPriv-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,49</t>
+          <t>0,89; 2,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,31</t>
+          <t>0,1; 1,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,46</t>
+          <t>0,0; 0,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,91</t>
+          <t>0,65; 1,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,44</t>
+          <t>0,31; 1,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,16</t>
+          <t>0,11; 1,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,2</t>
+          <t>0,24; 1,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,84</t>
+          <t>0,91; 1,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,04</t>
+          <t>0,34; 1,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,77</t>
+          <t>0,15; 0,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,73</t>
+          <t>0,16; 0,71</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -857,42 +857,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,85</t>
+          <t>1,34; 2,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,36</t>
+          <t>1,78; 3,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,26</t>
+          <t>1,09; 2,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,26</t>
+          <t>1,78; 3,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,68</t>
+          <t>1,31; 2,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,43</t>
+          <t>1,09; 2,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,72</t>
+          <t>0,67; 1,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,97</t>
+          <t>1,15; 2,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,64</t>
+          <t>1,6; 2,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 1,74</t>
+          <t>0,99; 1,8</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,42</t>
+          <t>1,6; 2,57</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,82</t>
+          <t>2,37; 5,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,0; 7,67</t>
+          <t>2,9; 7,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 9,39</t>
+          <t>4,66; 9,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,13</t>
+          <t>4,79; 8,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,4; 7,71</t>
+          <t>3,41; 7,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,08; 9,31</t>
+          <t>3,88; 9,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 8,28</t>
+          <t>4,35; 8,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,36; 10,12</t>
+          <t>6,0; 9,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 6,02</t>
+          <t>3,3; 5,79</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,02; 7,38</t>
+          <t>4,02; 7,36</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,83; 7,95</t>
+          <t>4,95; 7,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,84; 8,5</t>
+          <t>5,86; 8,54</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,73</t>
+          <t>1,68; 2,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1147,52 +1147,52 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,67</t>
+          <t>1,64; 2,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 3,41</t>
+          <t>2,36; 3,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,6</t>
+          <t>1,69; 2,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,48</t>
+          <t>1,43; 2,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,16</t>
+          <t>1,24; 2,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 2,99</t>
+          <t>2,08; 3,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,45</t>
+          <t>1,78; 2,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,45</t>
+          <t>1,7; 2,41</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,25</t>
+          <t>1,55; 2,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,0</t>
+          <t>2,38; 3,17</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>477</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4900</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8781; 25576</t>
+          <t>9141; 26816</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1019; 12742</t>
+          <t>1020; 13298</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 7354</t>
+          <t>0; 7069</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2380</t>
+          <t>0; 2405</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8414; 25043</t>
+          <t>8538; 24036</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4036; 19206</t>
+          <t>4110; 18170</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1272; 11494</t>
+          <t>1122; 10524</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1907; 9030</t>
+          <t>1966; 9200</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21672; 43141</t>
+          <t>21291; 44183</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7241; 23997</t>
+          <t>7844; 24256</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2405; 13362</t>
+          <t>2563; 14169</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2144; 9231</t>
+          <t>2221; 9964</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52481</t>
+          <t>55869</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31238</t>
+          <t>33238</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83719</t>
+          <t>89107</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23267; 48132</t>
+          <t>22641; 46753</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34853; 65913</t>
+          <t>34845; 65099</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21989; 46864</t>
+          <t>22687; 47014</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34156; 74580</t>
+          <t>39728; 77282</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19349; 42545</t>
+          <t>20750; 42435</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18586; 42750</t>
+          <t>19125; 44047</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12770; 34079</t>
+          <t>13255; 33185</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20716; 44121</t>
+          <t>25031; 45949</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48638; 81839</t>
+          <t>48483; 81931</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>60292; 98352</t>
+          <t>59627; 98720</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39772; 70608</t>
+          <t>40390; 73239</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>62157; 109573</t>
+          <t>70299; 113190</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39415</t>
+          <t>46279</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>52810</t>
+          <t>56600</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92225</t>
+          <t>102879</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13358; 32095</t>
+          <t>13055; 31242</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14429; 36894</t>
+          <t>13978; 36838</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25330; 51279</t>
+          <t>25436; 49707</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28008; 52582</t>
+          <t>34089; 61878</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16210; 36740</t>
+          <t>16268; 36778</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18713; 42716</t>
+          <t>17802; 41607</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23226; 45487</t>
+          <t>23912; 45820</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>42000; 66871</t>
+          <t>44108; 71499</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>33365; 61834</t>
+          <t>33916; 59548</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37765; 69328</t>
+          <t>37816; 69214</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52897; 87040</t>
+          <t>54194; 85129</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>76357; 111160</t>
+          <t>84740; 123489</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92361</t>
+          <t>102625</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>88283</t>
+          <t>94261</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>180644</t>
+          <t>196886</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>54737; 89218</t>
+          <t>55000; 88610</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>59320; 95835</t>
+          <t>59473; 95619</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53156; 90118</t>
+          <t>55333; 91305</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69537; 117775</t>
+          <t>82987; 130768</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>53667; 87804</t>
+          <t>57167; 90229</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48831; 88026</t>
+          <t>50951; 88039</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45793; 76045</t>
+          <t>43578; 77642</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>70133; 109175</t>
+          <t>77567; 113575</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>115980; 162688</t>
+          <t>118130; 166093</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>117070; 170972</t>
+          <t>118557; 168027</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>106281; 155511</t>
+          <t>107083; 152878</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>148520; 213200</t>
+          <t>172335; 229544</t>
         </is>
       </c>
     </row>
